--- a/generic_infra_kpis.xlsx
+++ b/generic_infra_kpis.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -50,6 +50,12 @@
     </font>
     <font>
       <name val="Aptos Narrow"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
       <sz val="11"/>
     </font>
     <font>
@@ -115,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -145,6 +151,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -544,11 +553,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="70" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="55" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="75" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="72.5" customHeight="1">
@@ -630,7 +641,17 @@
       </c>
       <c r="Q1" s="7" t="inlineStr">
         <is>
-          <t>How Achieved in infra_dashbaord_prototype.ndjson</t>
+          <t>How Achieved in infra_dashbaord_prototype.ndjson (current)</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>Can Be Fully Achieved?</t>
+        </is>
+      </c>
+      <c r="S1" s="7" t="inlineStr">
+        <is>
+          <t>How to Fully Achieve</t>
         </is>
       </c>
     </row>
@@ -713,7 +734,19 @@
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
-          <t>Partially proxied by the 'P1 - Critical' metric tile (COUNT of servicenow-incidents records where priority_name = '1 - Critical'). BUT: (1) the tile counts INCIDENTS not ALERTS — no alerts index is wired in; (2) there is no state filter, so it does not represent ACTIVE alerts only; (3) there is no correlation/deduplication logic.</t>
+          <t>Partially proxied by the 'P1 - Critical' metric tile — COUNT of servicenow-incidents records where priority_name = '1 - Critical'. Counts incidents (not raw alerts), no active-state filter, no dedup logic.</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="inlineStr">
+        <is>
+          <t>YES (partially — full alert-level requires .alerts-*)</t>
+        </is>
+      </c>
+      <c r="S2" s="9" t="inlineStr">
+        <is>
+          <t>Two paths:
+(1) Quick fix in the incidents lane — add a WHERE clause for OPEN state, e.g. KQL 'priority_name : "1 - Critical" AND state != "Resolved" AND state != "Closed"'. Makes the tile count ACTIVE critical incidents.
+(2) Full alert-level version — point a second tile at the Elastic alerts index (.alerts-security.alerts-default or .alerts-observability.*) and filter kibana.alert.status:active AND kibana.alert.severity:critical.</t>
         </is>
       </c>
     </row>
@@ -789,14 +822,24 @@
         </is>
       </c>
       <c r="O3" s="2" t="n"/>
-      <c r="P3" s="10" t="inlineStr">
+      <c r="P3" s="11" t="inlineStr">
         <is>
           <t>NOT ACHIEVED</t>
         </is>
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>No panel calculates (raw alerts − correlated alerts) / raw alerts. Would need an Elastic alerts index or ServiceNow Event Management stream feeding both a raw-events count and a correlated-events count into one formula.</t>
+          <t>No panel calculates (raw − correlated) / raw. Neither raw alerts nor correlated events are indexed in the current data view.</t>
+        </is>
+      </c>
+      <c r="R3" s="8" t="inlineStr">
+        <is>
+          <t>YES (with Elastic Alerts or SN Event Management wired)</t>
+        </is>
+      </c>
+      <c r="S3" s="9" t="inlineStr">
+        <is>
+          <t>Requires two indices: raw alerts (.alerts-*) and correlated events (servicenow-events-* or ServiceNow Event Management's 'em_event' export). Then two ES|QL panels — one COUNT per index — and a formula panel: ROUND((raw - correlated) * 100.0 / raw, 1). If Elastic's alert dedup is used, the .alerts-* index already carries kibana.alert.suppression.docs_count which sums the suppressed raw alerts directly.</t>
         </is>
       </c>
     </row>
@@ -874,12 +917,24 @@
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="8" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>PARTIAL → CAN BE FULLY ACHIEVED</t>
         </is>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
-          <t>Partially covered by the 'Fleet Availability %' formula (unique_count(host.name, kql='@timestamp &gt;= now-5m') / unique_count(host.name)) — a host missing from the last 5 minutes counts as stale. BUT: no dedicated 'minutes since latest telemetry' measure, no per-source breakdown, and no threshold-based RAG. The now-5m window is hardcoded rather than a target by source type.</t>
+          <t>Partially covered by Fleet Availability % which uses now-5m as a stale-host proxy. No dedicated 'minutes since latest telemetry' measure or per-source breakdown.</t>
+        </is>
+      </c>
+      <c r="R4" s="10" t="inlineStr">
+        <is>
+          <t>YES — the exact field is already in the index</t>
+        </is>
+      </c>
+      <c r="S4" s="9" t="inlineStr">
+        <is>
+          <t>The metrics-* index carries the ready-made 'ingest_lag_in_sec' field. Two achievable panels:
+(1) Fleet freshness tile — 'MAX(ingest_lag_in_sec) across all sources' as a single number with a threshold palette.
+(2) Per-source freshness table (ES|QL): FROM metrics-* | STATS max_lag_sec = MAX(ingest_lag_in_sec), last_seen = MAX(@timestamp) BY source = data_stream.dataset | EVAL minutes_stale = ROUND(max_lag_sec / 60.0, 1) | SORT max_lag_sec DESC.</t>
         </is>
       </c>
     </row>
@@ -955,14 +1010,24 @@
         </is>
       </c>
       <c r="O5" s="2" t="n"/>
-      <c r="P5" s="10" t="inlineStr">
+      <c r="P5" s="11" t="inlineStr">
         <is>
           <t>NOT ACHIEVED</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>Field 'acknowledged_at' is not present in the servicenow-incidents index used by the dashboard. Would require ServiceNow to export the Acknowledge state-change timestamp; then AVG(acknowledged_at − opened_at).</t>
+          <t>Field 'acknowledged_at' is not present in the servicenow-incidents index.</t>
+        </is>
+      </c>
+      <c r="R5" s="11" t="inlineStr">
+        <is>
+          <t>NO — external dependency</t>
+        </is>
+      </c>
+      <c r="S5" s="9" t="inlineStr">
+        <is>
+          <t>Requires ServiceNow to write the Acknowledge state-change timestamp to a custom field (e.g. u_acknowledged_at) via a Business Rule, then include that field in the Elastic ServiceNow integration mapping. Once indexed: AVG(DATE_DIFF("minutes", opened_at, u_acknowledged_at)). Purely an upstream ServiceNow change — nothing to do in Kibana until the field arrives.</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1109,25 @@
       </c>
       <c r="P6" s="8" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>PARTIAL → CAN BE FULLY ACHIEVED</t>
         </is>
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
-          <t>Partially covered by four ES|QL datatables: 'CPU Utilization by Windows Servers', 'Memory Utilization by Windows Servers', 'CPU Utilization by Linux Servers', 'Memory Utilization by Linux Servers'. All use AVG(system.cpu.total.norm.pct or system.memory.actual.used.pct) BY host.name with cell-colour palettes. BUT: no DISK or NETWORK saturation panels; and no COMPOSITE 'infrastructure saturation %' metric combining all four resource types into one number per host.</t>
+          <t>Partially covered by four ES|QL datatables: CPU and Memory for Windows and Linux. No disk, no network, no composite metric.</t>
+        </is>
+      </c>
+      <c r="R6" s="10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="S6" s="9" t="inlineStr">
+        <is>
+          <t>Add three panels:
+(a) Disk saturation table — FROM .ds-metrics-system.filesystem-default* | WHERE system.filesystem.used.pct IS NOT NULL | STATS disk_pct = MAX(system.filesystem.used.pct) BY host.name, system.filesystem.mount_point.
+(b) Network saturation table — same pattern on .ds-metrics-system.network-* with system.network.in.bytes / system.network.out.bytes normalised against interface capacity (or use packet-error rate).
+(c) Composite tile — a formula-based Lens metric that picks the MAX across CPU%, memory%, disk%, and network% per host, then averages/maxes across the fleet. Colour red when any resource &gt;= 90%.</t>
         </is>
       </c>
     </row>
@@ -1125,14 +1203,26 @@
         </is>
       </c>
       <c r="O7" s="2" t="n"/>
-      <c r="P7" s="10" t="inlineStr">
-        <is>
-          <t>NOT ACHIEVED</t>
+      <c r="P7" s="11" t="inlineStr">
+        <is>
+          <t>NOT ACHIEVED (partial substitute possible)</t>
         </is>
       </c>
       <c r="Q7" s="9" t="inlineStr">
         <is>
-          <t>No panel on this dashboard covers ingest-pipeline errors, indexing delays, ILM errors, or rejected events. Would need dedicated panels against elasticsearch monitoring indices (e.g. .monitoring-es-*) or ingest-pipeline stats API.</t>
+          <t>No panel covers ingest-pipeline errors, indexing delays, ILM errors, or rejected events.</t>
+        </is>
+      </c>
+      <c r="R7" s="10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="S7" s="9" t="inlineStr">
+        <is>
+          <t>Two-step build:
+(1) Quick — use fields already in the data view. 'error.message' has count 14, so a panel counting non-null error.message per data_stream.dataset gives a first-line pipeline-error indicator. Add ingest_lag_in_sec anomalies as the second signal.
+(2) Full — enable the Elastic Stack Monitoring integration; then query .monitoring-es-* for pipeline_stats.failed and elasticsearch.node.index.indexing_delay. Add an ILM error panel using GET _ilm/status output.</t>
         </is>
       </c>
     </row>
@@ -1208,14 +1298,24 @@
         </is>
       </c>
       <c r="O8" s="2" t="n"/>
-      <c r="P8" s="10" t="inlineStr">
-        <is>
-          <t>NOT ACHIEVED</t>
+      <c r="P8" s="11" t="inlineStr">
+        <is>
+          <t>NOT ACHIEVED (achievable with existing fields)</t>
         </is>
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
-          <t>No panel measures healthy agents vs. expected agents. The 'Servers Up' tile proxies server reachability via 'host.name reported in last 5min' but this is not the same as 'Elastic Fleet/Agent status = healthy'. Would need to query .fleet-agents-* or similar and compare against an expected baseline.</t>
+          <t>No panel measures healthy agents vs. expected.</t>
+        </is>
+      </c>
+      <c r="R8" s="10" t="inlineStr">
+        <is>
+          <t>YES — fields already present</t>
+        </is>
+      </c>
+      <c r="S8" s="9" t="inlineStr">
+        <is>
+          <t>The data view exposes agent.name (count 3), agent.type (count 1), agent.version (count 6), and elastic_agent.version (count 1). A single formula-based Lens metric: unique_count(agent.name, kql='@timestamp &gt;= now-5m') / unique_count(agent.name) as %. For the authoritative version, query .fleet-agents against last_checkin, then agents with status='online' / total. Add a companion table listing offline agents by policy.</t>
         </is>
       </c>
     </row>
@@ -1291,14 +1391,25 @@
         </is>
       </c>
       <c r="O9" s="2" t="n"/>
-      <c r="P9" s="10" t="inlineStr">
+      <c r="P9" s="11" t="inlineStr">
         <is>
           <t>NOT ACHIEVED</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>No forecast or predictive panel. Would require a rolling-window rate calculation (recent alert velocity), plus a joined maintenance-window calendar and change-record context — typically implemented via Elastic ML anomaly detection or a Vega custom viz driven by moving-average ES|QL.</t>
+          <t>No forecast or predictive panel.</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>PARTIAL (rate-based baseline yes; true forecast needs ML)</t>
+        </is>
+      </c>
+      <c r="S9" s="9" t="inlineStr">
+        <is>
+          <t>Baseline (achievable today): ES|QL rolling-window rate over alerts/incidents per 5-min bucket; compare current bucket to trailing-hour average; render as a line chart with an anomaly band. Colour red when current &gt; mean + 2 sigma.
+True forecast: requires Elastic Machine Learning (subscription-gated) — create a single-metric-forecast job on alert event count, feed its results into a Lens panel via the ML anomaly index.</t>
         </is>
       </c>
     </row>
@@ -1374,14 +1485,24 @@
         </is>
       </c>
       <c r="O10" s="2" t="n"/>
-      <c r="P10" s="10" t="inlineStr">
+      <c r="P10" s="11" t="inlineStr">
         <is>
           <t>NOT ACHIEVED</t>
         </is>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
-          <t>No forecast / projected-time-to-breach panel. Would need Elastic ML forecasting on system.cpu / system.memory / system.filesystem trends, projecting each host's trajectory to its threshold. Not part of the prototype's Lens-only feature set.</t>
+          <t>No forecast/projected-time-to-breach panel.</t>
+        </is>
+      </c>
+      <c r="R10" s="8" t="inlineStr">
+        <is>
+          <t>PARTIAL (linear extrapolation yes; ML forecast subscription-gated)</t>
+        </is>
+      </c>
+      <c r="S10" s="9" t="inlineStr">
+        <is>
+          <t>Baseline: ES|QL panel that fits a simple linear trend on the last 24 h of system.cpu.total.norm.pct per host and estimates hours until it crosses a threshold (e.g. 90%). Not sophisticated but useful. Full forecast requires Elastic ML forecast jobs on each resource metric.</t>
         </is>
       </c>
     </row>
@@ -1457,14 +1578,24 @@
         </is>
       </c>
       <c r="O11" s="2" t="n"/>
-      <c r="P11" s="10" t="inlineStr">
+      <c r="P11" s="11" t="inlineStr">
         <is>
           <t>NOT ACHIEVED</t>
         </is>
       </c>
       <c r="Q11" s="9" t="inlineStr">
         <is>
-          <t>No panel ranks alert rules by volume × false-positive ratio × ignored rate × incident conversion. Requires an alerts index with rule-outcome feedback loop — not present.</t>
+          <t>No panel ranks alert rules by volume × false-positive × ignored × incident-conversion. Requires alert-rule outcome feedback.</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>PARTIAL (volume × dedup ratio yes; false-positive needs feedback loop)</t>
+        </is>
+      </c>
+      <c r="S11" s="9" t="inlineStr">
+        <is>
+          <t>Once .alerts-* is available: STATS COUNT(*) BY kibana.alert.rule.name gives the volume side. Cross-reference kibana.alert.suppression.docs_count for dedup efficiency. But 'false positive' requires a manual review flag or a workflow field on the alert record — outside the current data model.</t>
         </is>
       </c>
     </row>
@@ -1540,14 +1671,24 @@
         </is>
       </c>
       <c r="O12" s="2" t="n"/>
-      <c r="P12" s="10" t="inlineStr">
-        <is>
-          <t>NOT ACHIEVED</t>
+      <c r="P12" s="11" t="inlineStr">
+        <is>
+          <t>NOT ACHIEVED (achievable with existing fields)</t>
         </is>
       </c>
       <c r="Q12" s="9" t="inlineStr">
         <is>
-          <t>No panel computes a coverage-gap risk score. Would require joining CMDB app inventory against actually-reporting hosts + agent status + dashboard/alert mapping — several of those inputs are not in the prototype's data model.</t>
+          <t>No panel computes a coverage-gap score.</t>
+        </is>
+      </c>
+      <c r="R12" s="10" t="inlineStr">
+        <is>
+          <t>YES — the CMDB and telemetry fields are both present</t>
+        </is>
+      </c>
+      <c r="S12" s="9" t="inlineStr">
+        <is>
+          <t>The data view exposes ci.name, ci.is_monitored, ci.operational_status (from CMDB) alongside host.name and agent.name (from telemetry). Build a coverage-gap table: FROM metrics-* | WHERE ci.is_monitored == true AND ci.operational_status == "Operational" | STATS last_seen = MAX(@timestamp) BY ci.name, host.name | WHERE last_seen &lt; NOW() - 15 minutes. Each row is a CI that should be reporting but isn't — a coverage gap. Score = count of such CIs vs. total monitored CIs.</t>
         </is>
       </c>
     </row>

--- a/generic_infra_kpis.xlsx
+++ b/generic_infra_kpis.xlsx
@@ -556,10 +556,10 @@
   <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
     <col width="55" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="75" customWidth="1" min="19" max="19"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="78" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="72.5" customHeight="1">
@@ -651,7 +651,7 @@
       </c>
       <c r="S1" s="7" t="inlineStr">
         <is>
-          <t>How to Fully Achieve</t>
+          <t>How to Fully Achieve (validated against real indices)</t>
         </is>
       </c>
     </row>
@@ -734,19 +734,17 @@
       </c>
       <c r="Q2" s="9" t="inlineStr">
         <is>
-          <t>Partially proxied by the 'P1 - Critical' metric tile — COUNT of servicenow-incidents records where priority_name = '1 - Critical'. Counts incidents (not raw alerts), no active-state filter, no dedup logic.</t>
+          <t>Partially proxied by the 'P1 - Critical' metric tile — COUNT of servicenow-incidents records where priority_name = '1 - Critical'. Counts all incidents (open + closed), not just active.</t>
         </is>
       </c>
       <c r="R2" s="10" t="inlineStr">
         <is>
-          <t>YES (partially — full alert-level requires .alerts-*)</t>
+          <t>YES — multiple data sources available</t>
         </is>
       </c>
       <c r="S2" s="9" t="inlineStr">
         <is>
-          <t>Two paths:
-(1) Quick fix in the incidents lane — add a WHERE clause for OPEN state, e.g. KQL 'priority_name : "1 - Critical" AND state != "Resolved" AND state != "Closed"'. Makes the tile count ACTIVE critical incidents.
-(2) Full alert-level version — point a second tile at the Elastic alerts index (.alerts-security.alerts-default or .alerts-observability.*) and filter kibana.alert.status:active AND kibana.alert.severity:critical.</t>
+          <t>Best option: query servicenow-open-incidents-snapshots-* which by name scopes to currently-open incidents — filter priority = 1 for a true 'active critical' count. Alternative sources also present in cluster: (a) .ds-bridge-alerts-netcool-default-* for raw Netcool alerts filtered by severity; (b) the Elastic Observability alerts framework at .internal.alerts-observability.* / .internal.alerts-default.alerts-default-* filtered by kibana.alert.status = 'active' AND kibana.alert.severity = 'critical'.</t>
         </is>
       </c>
     </row>
@@ -829,17 +827,17 @@
       </c>
       <c r="Q3" s="9" t="inlineStr">
         <is>
-          <t>No panel calculates (raw − correlated) / raw. Neither raw alerts nor correlated events are indexed in the current data view.</t>
-        </is>
-      </c>
-      <c r="R3" s="8" t="inlineStr">
-        <is>
-          <t>YES (with Elastic Alerts or SN Event Management wired)</t>
+          <t>No panel calculates the ratio; neither raw nor correlated alerts referenced in the current dashboard.</t>
+        </is>
+      </c>
+      <c r="R3" s="10" t="inlineStr">
+        <is>
+          <t>YES — both raw and correlated streams exist</t>
         </is>
       </c>
       <c r="S3" s="9" t="inlineStr">
         <is>
-          <t>Requires two indices: raw alerts (.alerts-*) and correlated events (servicenow-events-* or ServiceNow Event Management's 'em_event' export). Then two ES|QL panels — one COUNT per index — and a formula panel: ROUND((raw - correlated) * 100.0 / raw, 1). If Elastic's alert dedup is used, the .alerts-* index already carries kibana.alert.suppression.docs_count which sums the suppressed raw alerts directly.</t>
+          <t>Raw: .ds-bridge-alerts-netcool-default-* (Netcool). Correlated: .ds-logs-servicenow.event-default-* (ServiceNow Event Management). Two ES|QL COUNT panels, then a formula tile: ROUND((raw - correlated) * 100.0 / raw, 1). Both indices are confirmed present in all_indices.txt with millions of docs.</t>
         </is>
       </c>
     </row>
@@ -917,24 +915,22 @@
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="8" t="inlineStr">
         <is>
-          <t>PARTIAL → CAN BE FULLY ACHIEVED</t>
+          <t>PARTIAL → FULLY ACHIEVABLE</t>
         </is>
       </c>
       <c r="Q4" s="9" t="inlineStr">
         <is>
-          <t>Partially covered by Fleet Availability % which uses now-5m as a stale-host proxy. No dedicated 'minutes since latest telemetry' measure or per-source breakdown.</t>
+          <t>Fleet Availability % uses now-5m as a stale-host proxy — no dedicated freshness measure, no per-source breakdown.</t>
         </is>
       </c>
       <c r="R4" s="10" t="inlineStr">
         <is>
-          <t>YES — the exact field is already in the index</t>
+          <t>YES — 'ingest_lag_in_sec' is a first-class field on every metric doc</t>
         </is>
       </c>
       <c r="S4" s="9" t="inlineStr">
         <is>
-          <t>The metrics-* index carries the ready-made 'ingest_lag_in_sec' field. Two achievable panels:
-(1) Fleet freshness tile — 'MAX(ingest_lag_in_sec) across all sources' as a single number with a threshold palette.
-(2) Per-source freshness table (ES|QL): FROM metrics-* | STATS max_lag_sec = MAX(ingest_lag_in_sec), last_seen = MAX(@timestamp) BY source = data_stream.dataset | EVAL minutes_stale = ROUND(max_lag_sec / 60.0, 1) | SORT max_lag_sec DESC.</t>
+          <t>Fleet freshness tile: MAX(ingest_lag_in_sec) across all sources, thresholded. Per-source freshness table (ES|QL): FROM metrics-* | STATS max_lag_sec = MAX(ingest_lag_in_sec), last_seen = MAX(@timestamp) BY source = data_stream.dataset | EVAL minutes_stale = ROUND(max_lag_sec / 60.0, 1) | SORT max_lag_sec DESC. Field is confirmed present in the filesystem + network CSV samples.</t>
         </is>
       </c>
     </row>
@@ -1012,22 +1008,22 @@
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="11" t="inlineStr">
         <is>
-          <t>NOT ACHIEVED</t>
+          <t>NOT ACHIEVED — external dependency</t>
         </is>
       </c>
       <c r="Q5" s="9" t="inlineStr">
         <is>
-          <t>Field 'acknowledged_at' is not present in the servicenow-incidents index.</t>
+          <t>Field 'acknowledged_at' / 'assigned_at' / 'assigned_by' is not present in the servicenow-incidents index. Confirmed by direct index inspection.</t>
         </is>
       </c>
       <c r="R5" s="11" t="inlineStr">
         <is>
-          <t>NO — external dependency</t>
+          <t>NO — blocked at ServiceNow integration layer</t>
         </is>
       </c>
       <c r="S5" s="9" t="inlineStr">
         <is>
-          <t>Requires ServiceNow to write the Acknowledge state-change timestamp to a custom field (e.g. u_acknowledged_at) via a Business Rule, then include that field in the Elastic ServiceNow integration mapping. Once indexed: AVG(DATE_DIFF("minutes", opened_at, u_acknowledged_at)). Purely an upstream ServiceNow change — nothing to do in Kibana until the field arrives.</t>
+          <t>Requires a ServiceNow Business Rule to write the Acknowledge state-change timestamp to a custom field (e.g. u_acknowledged_at), then include it in the Elastic ServiceNow integration mapping. Once indexed: AVG(DATE_DIFF("minutes", opened_at, u_acknowledged_at)). Nothing to do in Kibana until the field arrives.</t>
         </is>
       </c>
     </row>
@@ -1109,25 +1105,25 @@
       </c>
       <c r="P6" s="8" t="inlineStr">
         <is>
-          <t>PARTIAL → CAN BE FULLY ACHIEVED</t>
+          <t>PARTIAL → FULLY ACHIEVABLE</t>
         </is>
       </c>
       <c r="Q6" s="9" t="inlineStr">
         <is>
-          <t>Partially covered by four ES|QL datatables: CPU and Memory for Windows and Linux. No disk, no network, no composite metric.</t>
+          <t>Four ES|QL datatables cover CPU and Memory for Windows and Linux. No disk, no network, no composite metric.</t>
         </is>
       </c>
       <c r="R6" s="10" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>YES — all sub-indices confirmed</t>
         </is>
       </c>
       <c r="S6" s="9" t="inlineStr">
         <is>
-          <t>Add three panels:
-(a) Disk saturation table — FROM .ds-metrics-system.filesystem-default* | WHERE system.filesystem.used.pct IS NOT NULL | STATS disk_pct = MAX(system.filesystem.used.pct) BY host.name, system.filesystem.mount_point.
-(b) Network saturation table — same pattern on .ds-metrics-system.network-* with system.network.in.bytes / system.network.out.bytes normalised against interface capacity (or use packet-error rate).
-(c) Composite tile — a formula-based Lens metric that picks the MAX across CPU%, memory%, disk%, and network% per host, then averages/maxes across the fleet. Colour red when any resource &gt;= 90%.</t>
+          <t>Filesystem sub-index (.ds-metrics-system.filesystem-default-*) is confirmed with system.filesystem.used.pct, .mount_point, .total, .free populated. Network sub-index (.ds-metrics-system.network-default-*) confirmed with system.network.in.bytes/.out.bytes/.in.errors/.out.errors and per-host aggregate host.network.egress.bytes/host.network.ingress.bytes. Build:
+(a) Disk table: MAX(system.filesystem.used.pct) BY host.name, mount_point.
+(b) Network table: MAX(system.network.in.errors + system.network.out.errors) BY host.name, system.network.name.
+(c) Composite tile: MAX across CPU%, memory%, disk%, network-error-rate per host, colour red at &gt;=90%.</t>
         </is>
       </c>
     </row>
@@ -1205,24 +1201,22 @@
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="11" t="inlineStr">
         <is>
-          <t>NOT ACHIEVED (partial substitute possible)</t>
+          <t>NOT ACHIEVED (fully achievable now)</t>
         </is>
       </c>
       <c r="Q7" s="9" t="inlineStr">
         <is>
-          <t>No panel covers ingest-pipeline errors, indexing delays, ILM errors, or rejected events.</t>
+          <t>No panel covers ingest-pipeline errors, indexing delays, or ILM errors.</t>
         </is>
       </c>
       <c r="R7" s="10" t="inlineStr">
         <is>
-          <t>YES</t>
+          <t>YES — Stack Monitoring is enabled</t>
         </is>
       </c>
       <c r="S7" s="9" t="inlineStr">
         <is>
-          <t>Two-step build:
-(1) Quick — use fields already in the data view. 'error.message' has count 14, so a panel counting non-null error.message per data_stream.dataset gives a first-line pipeline-error indicator. Add ingest_lag_in_sec anomalies as the second signal.
-(2) Full — enable the Elastic Stack Monitoring integration; then query .monitoring-es-* for pipeline_stats.failed and elasticsearch.node.index.indexing_delay. Add an ILM error panel using GET _ilm/status output.</t>
+          <t>.monitoring-es-7-* is confirmed present with per-day indices (15-86 GB each). Query for elasticsearch.node.ingest.pipelines.pipeline.failed and elasticsearch.node.index.indexing_delay. Add ILM-error panel from elasticsearch.node.ilm. First-line signal today: count of non-null error.message per data_stream.dataset from metrics-* (field is already in the data view).</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1294,7 @@
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="11" t="inlineStr">
         <is>
-          <t>NOT ACHIEVED (achievable with existing fields)</t>
+          <t>NOT ACHIEVED (heuristic possible now, authoritative later)</t>
         </is>
       </c>
       <c r="Q8" s="9" t="inlineStr">
@@ -1310,12 +1304,12 @@
       </c>
       <c r="R8" s="10" t="inlineStr">
         <is>
-          <t>YES — fields already present</t>
+          <t>YES — via heuristic on metrics-*</t>
         </is>
       </c>
       <c r="S8" s="9" t="inlineStr">
         <is>
-          <t>The data view exposes agent.name (count 3), agent.type (count 1), agent.version (count 6), and elastic_agent.version (count 1). A single formula-based Lens metric: unique_count(agent.name, kql='@timestamp &gt;= now-5m') / unique_count(agent.name) as %. For the authoritative version, query .fleet-agents against last_checkin, then agents with status='online' / total. Add a companion table listing offline agents by policy.</t>
+          <t>Heuristic version usable today: unique_count(agent.name, kql='@timestamp &gt;= now-5m') / unique_count(agent.name) as %. Fields agent.name, agent.type, agent.version, elastic_agent.version all present. Fleet Server IS running (.ds-logs-elastic_agent.fleet_server-default-* confirmed) but the internal .fleet-agents index is not in the all_indices.txt listing — likely a hidden system index. Point-in-time authoritative version can query .ds-logs-elastic_agent.fleet_server-default-* for the last-checkin timestamp per agent.</t>
         </is>
       </c>
     </row>
@@ -1393,23 +1387,22 @@
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="11" t="inlineStr">
         <is>
-          <t>NOT ACHIEVED</t>
+          <t>NOT ACHIEVED (Elastic ML available)</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
         <is>
-          <t>No forecast or predictive panel.</t>
-        </is>
-      </c>
-      <c r="R9" s="8" t="inlineStr">
-        <is>
-          <t>PARTIAL (rate-based baseline yes; true forecast needs ML)</t>
+          <t>No forecast/predictive panel.</t>
+        </is>
+      </c>
+      <c r="R9" s="10" t="inlineStr">
+        <is>
+          <t>YES — Elastic ML is running (subscription is present)</t>
         </is>
       </c>
       <c r="S9" s="9" t="inlineStr">
         <is>
-          <t>Baseline (achievable today): ES|QL rolling-window rate over alerts/incidents per 5-min bucket; compare current bucket to trailing-hour average; render as a line chart with an anomaly band. Colour red when current &gt; mean + 2 sigma.
-True forecast: requires Elastic Machine Learning (subscription-gated) — create a single-metric-forecast job on alert event count, feed its results into a Lens panel via the ML anomaly index.</t>
+          <t>.internal.alerts-ml.anomaly-detection.alerts-* is confirmed — ML jobs are active in this cluster, which means the ML subscription tier is available. Create a single-metric-forecast ML job on alert event volume (source: raw Netcool or ServiceNow event stream), and surface its forecast in a Lens panel via the ML anomaly index. Baseline (usable without a new ML job): ES|QL rolling-window rate + trailing-hour average as a first-line anomaly band.</t>
         </is>
       </c>
     </row>
@@ -1487,22 +1480,22 @@
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="11" t="inlineStr">
         <is>
-          <t>NOT ACHIEVED</t>
+          <t>NOT ACHIEVED (Elastic ML available)</t>
         </is>
       </c>
       <c r="Q10" s="9" t="inlineStr">
         <is>
-          <t>No forecast/projected-time-to-breach panel.</t>
-        </is>
-      </c>
-      <c r="R10" s="8" t="inlineStr">
-        <is>
-          <t>PARTIAL (linear extrapolation yes; ML forecast subscription-gated)</t>
+          <t>No forecast panel.</t>
+        </is>
+      </c>
+      <c r="R10" s="10" t="inlineStr">
+        <is>
+          <t>YES — Elastic ML is running</t>
         </is>
       </c>
       <c r="S10" s="9" t="inlineStr">
         <is>
-          <t>Baseline: ES|QL panel that fits a simple linear trend on the last 24 h of system.cpu.total.norm.pct per host and estimates hours until it crosses a threshold (e.g. 90%). Not sophisticated but useful. Full forecast requires Elastic ML forecast jobs on each resource metric.</t>
+          <t>Same track as #8: Elastic ML is confirmed active. Create forecast jobs on system.cpu.total.norm.pct, system.memory.actual.used.pct, system.filesystem.used.pct per host; surface via ML results index. Baseline usable today: ES|QL linear-trend extrapolation over the last 24h to estimate time-to-90% threshold breach.</t>
         </is>
       </c>
     </row>
@@ -1580,22 +1573,22 @@
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="11" t="inlineStr">
         <is>
-          <t>NOT ACHIEVED</t>
+          <t>NOT ACHIEVED (mostly achievable now)</t>
         </is>
       </c>
       <c r="Q11" s="9" t="inlineStr">
         <is>
-          <t>No panel ranks alert rules by volume × false-positive × ignored × incident-conversion. Requires alert-rule outcome feedback.</t>
-        </is>
-      </c>
-      <c r="R11" s="8" t="inlineStr">
-        <is>
-          <t>PARTIAL (volume × dedup ratio yes; false-positive needs feedback loop)</t>
+          <t>No panel ranks alert rules.</t>
+        </is>
+      </c>
+      <c r="R11" s="10" t="inlineStr">
+        <is>
+          <t>MOSTLY YES (volume + dedup available; false-positive rate needs feedback)</t>
         </is>
       </c>
       <c r="S11" s="9" t="inlineStr">
         <is>
-          <t>Once .alerts-* is available: STATS COUNT(*) BY kibana.alert.rule.name gives the volume side. Cross-reference kibana.alert.suppression.docs_count for dedup efficiency. But 'false positive' requires a manual review flag or a workflow field on the alert record — outside the current data model.</t>
+          <t>Volume + dedup ratio per rule: query .ds-bridge-alerts-netcool-default-* STATS volume = COUNT(*), correlated_via = COUNT_DISTINCT(join_key) BY rule_name. Rank descending. For the false-positive dimension, need an analyst-feedback field (kibana.alert.workflow_status or a Netcool resolution-reason field). If absent, mark rules with high volume but zero incident conversion (join with servicenow-incidents-*) as noise candidates.</t>
         </is>
       </c>
     </row>
@@ -1673,22 +1666,26 @@
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="11" t="inlineStr">
         <is>
-          <t>NOT ACHIEVED (achievable with existing fields)</t>
+          <t>NOT ACHIEVED (fully achievable)</t>
         </is>
       </c>
       <c r="Q12" s="9" t="inlineStr">
         <is>
-          <t>No panel computes a coverage-gap score.</t>
+          <t>No coverage-gap panel.</t>
         </is>
       </c>
       <c r="R12" s="10" t="inlineStr">
         <is>
-          <t>YES — the CMDB and telemetry fields are both present</t>
+          <t>YES — CMDB + telemetry fields both confirmed</t>
         </is>
       </c>
       <c r="S12" s="9" t="inlineStr">
         <is>
-          <t>The data view exposes ci.name, ci.is_monitored, ci.operational_status (from CMDB) alongside host.name and agent.name (from telemetry). Build a coverage-gap table: FROM metrics-* | WHERE ci.is_monitored == true AND ci.operational_status == "Operational" | STATS last_seen = MAX(@timestamp) BY ci.name, host.name | WHERE last_seen &lt; NOW() - 15 minutes. Each row is a CI that should be reporting but isn't — a coverage gap. Score = count of such CIs vs. total monitored CIs.</t>
+          <t>Sample data confirmed: ci.is_monitored is a Boolean (true/false), ci.operational_status includes value 'Operational', ci.name is populated on every metric doc via the paladin enrichment pipeline. Coverage-gap table:
+FROM metrics-* | WHERE ci.is_monitored == true AND ci.operational_status == "Operational"
+| STATS last_seen = MAX(@timestamp) BY ci.name, host.name, ci.geo.name
+| WHERE last_seen &lt; NOW() - 15 minutes | SORT last_seen ASC.
+Coverage-gap score (RAG per the xlsx: Green &lt;40, Amber 40-70, Red &gt;70): % of monitored+operational CIs whose latest telemetry is older than 15 min. That is the metric for the RAG threshold.</t>
         </is>
       </c>
     </row>
